--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134859681</v>
+        <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>92667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,31 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>3884</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1293,13 +1296,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576054</v>
+        <v>576012</v>
       </c>
       <c r="R7" t="n">
-        <v>6407792</v>
+        <v>6407748</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1323,17 +1326,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosök, stubbe</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,6 +1340,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,52 +1358,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134859681</t>
+          <t>https://artportalen.se/Sighting/136715456</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135046379</v>
+        <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>58141</v>
+        <v>92667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1412,13 +1410,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576240</v>
+        <v>576047</v>
       </c>
       <c r="R8" t="n">
-        <v>6407794</v>
+        <v>6407754</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,12 +1440,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,6 +1454,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,50 +1472,46 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135046379</t>
+          <t>https://artportalen.se/Sighting/136715476</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135046394</v>
+        <v>134859681</v>
       </c>
       <c r="B9" t="n">
-        <v>58141</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1526,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576213</v>
+        <v>576054</v>
       </c>
       <c r="R9" t="n">
-        <v>6407847</v>
+        <v>6407792</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1556,12 +1551,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök, stubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,6 +1586,234 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134859681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135046379</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>576240</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6407794</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135046379</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135046394</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 28505, Dröppstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>576213</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6407847</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135046394</t>
         </is>
@@ -1601,6 +1829,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92667</v>
+        <v>92672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92667</v>
+        <v>92672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92672</v>
+        <v>92674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92672</v>
+        <v>92674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92674</v>
+        <v>92676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92674</v>
+        <v>92676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92676</v>
+        <v>92678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92678</v>
+        <v>92679</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92679</v>
+        <v>92685</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92679</v>
+        <v>92685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92685</v>
+        <v>92689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92685</v>
+        <v>92689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92689</v>
+        <v>92691</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92689</v>
+        <v>92691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92691</v>
+        <v>92704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92691</v>
+        <v>92704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92704</v>
+        <v>92706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92704</v>
+        <v>92706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92706</v>
+        <v>92709</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92706</v>
+        <v>92709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28505-2026 artfynd.xlsx
+++ b/artfynd/A 28505-2026 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>136715456</v>
       </c>
       <c r="B7" t="n">
-        <v>92709</v>
+        <v>92719</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>136715476</v>
       </c>
       <c r="B8" t="n">
-        <v>92709</v>
+        <v>92719</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
